--- a/astro-site/public/dl/kit-tareas-pizzeria/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-pizzeria/BONUS-02-calendario-anual-tareas.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario Anual'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -121,44 +123,44 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -518,13 +520,13 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -573,8 +575,25 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pizzeria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -583,15 +602,15 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="15"/>
-    <col customWidth="1" max="2" min="2" width="25"/>
-    <col customWidth="1" max="3" min="3" width="40"/>
-    <col customWidth="1" max="4" min="4" width="20"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1114,7 +1133,15 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A29:D29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pizzeria/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-pizzeria/BONUS-02-calendario-anual-tareas.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario Anual'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Calendario Anual'!$A$1:$D$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,8 +74,22 @@
       <color rgb="00888888"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +112,21 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -155,6 +186,54 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -522,64 +601,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>BONUS: Calendario Anual de Tareas Especiales</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>▸ Consulta las fechas clave de hostelería mes a mes</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>▸ Planifica con antelación: menús especiales, decoración, stock</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>▸ Añade las fechas relevantes de tu zona (fiestas locales, ferias)</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes · AI Chef Pro · aichef.pro</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pizzeria · info@aichef.pro</t>
+    <row r="12" ht="16" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>▸ Estás en BONUS-02-calendario-anual-tareas.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Pizzería · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="35" customHeight="1">
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pizzeria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -604,13 +739,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -651,487 +789,702 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Enero</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>1 Ene — Año Nuevo</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Menú brunch recuperación, stock reducido</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Decidir si se abre; si se cierra, comunicarlo en Google Business Profile, en la web y en las apps de delivery con 1 semana</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="19" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Enero</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>6 Ene — Reyes</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Roscón de Reyes, menú familiar</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="19" t="n"/>
+      <c r="G6" s="19" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Febrero</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>14 Feb — San Valentín</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>Menú parejas, decoración romántica, turnos extra</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="19" t="n"/>
+      <c r="G7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Febrero</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Carnaval (variable)</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>Menú temático, decoración, disfraces equipo</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="19" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Marzo</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>19 Mar — Día del Padre</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Menú familiar de mediodía, reservas ampliadas y pizza XL para compartir</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>2 semanas</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Marzo-Abril</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>Semana Santa (variable)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>Menú de vigilia, bacalao, potaje, torrijas</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Marzo-Abril</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Apertura terraza</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Montaje, licencia, carta exterior</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>1 mes</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Abril-Junio</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Comuniones y bautizos (temporada)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Menú de grupo cerrado, señal y precio por comensal, sala o terraza privatizada</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>1 mes</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Mayo</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>1 Mayo — Día del Trabajo</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Servicio de festivo, turnos especiales</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Mayo</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>Primer domingo — Día de la Madre</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>Menú especial, reservas ampliadas, detalle</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Junio</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Inicio temporada alta</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>Refuerzo de plantilla, stock verano</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>1 mes</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Junio</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>24 Jun — San Juan</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>Menú especial, terraza nocturna</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Julio-Agosto</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Temporada alta</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>Personal extra, horarios ampliados, carta verano</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>15 Ago — Asunción</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>Servicio de festivo, refuerzo de turnos y de repartidores, terraza a pleno rendimiento</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Vuelta al cole / rutina</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>Carta otoño, menú del día reforzado</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Octubre</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>31 Oct — Halloween</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>Decoración temática, menú/cocktails especiales</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>1 Nov — Todos los Santos</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Comida familiar de mediodía, pizza de temporada (setas, calabaza, castañas)</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>Cierre terraza</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>Recoger mobiliario, inventario, reparaciones</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>6-8 Dic — Puente de la Constitución y la Inmaculada</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Horario de festivo, refuerzo de mediodía y de delivery, masa y stock para tres días seguidos</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>2 semanas</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>Cenas de empresa</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>Menú de grupo, reservas grandes, turnos extra</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>1 mes</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="19" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>24-25 Dic — Nochebuena/Navidad</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>Menú navideño, decoración, stock especial</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>31 Dic — Nochevieja</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>Menú gala, cotillón, uvas, cava, turnos noche</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr"/>
-      <c r="B22" s="10" t="inlineStr"/>
-      <c r="C22" s="10" t="inlineStr"/>
-      <c r="D22" s="9" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="19" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="n"/>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>(Tu fecha)</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>(Añade aquí)</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>(Tareas específicas)</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>(Antelación)</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="19" t="n"/>
+      <c r="G28" s="19" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>(Tu fecha)</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>(Añade aquí)</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C29" s="25" t="inlineStr">
         <is>
           <t>(Tareas específicas)</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>(Antelación)</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="19" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>(Tu fecha)</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>(Añade aquí)</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>(Tareas específicas)</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>(Antelación)</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="19" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>(Tu fecha)</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>(Añade aquí)</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C31" s="25" t="inlineStr">
         <is>
           <t>(Tareas específicas)</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>(Antelación)</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>(Tu fecha)</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>(Añade aquí)</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C32" s="25" t="inlineStr">
         <is>
           <t>(Tareas específicas)</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes · AI Chef Pro · aichef.pro —</t>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>(Antelación)</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="19" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Pizzería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="2">
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A29:D29"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
